--- a/data/checklists/nba/1993-94-SkyBox-Premium-Basketball.xlsx
+++ b/data/checklists/nba/1993-94-SkyBox-Premium-Basketball.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D336"/>
+  <dimension ref="A1:D475"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6460,6 +6460,2444 @@
       </c>
       <c r="D336" t="inlineStr"/>
     </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>Jim Jackson</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>Dallas Mavericks</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>1992-93 SkyBox Draft Picks Update</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr"/>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>Doug Christie</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>Seattle SuperSonics</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>1992-93 SkyBox Draft Picks Update</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr"/>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>Michael Jordan</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>Chicago Bulls</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>Center Stage</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr"/>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>Shaquille O'Neal</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>Orlando Magic</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>Center Stage</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr"/>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>Charles Barkley</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>Phoenix Suns</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>Center Stage</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr"/>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>John Starks</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>New York Knicks</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>Center Stage</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr"/>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>Larry Johnson</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>Charlotte Hornets</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>Center Stage</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr"/>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>Hakeem Olajuwon</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>Houston Rockets</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>Center Stage</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr"/>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>Kenny Anderson</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>New Jersey Nets</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>Center Stage</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr"/>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>Mahmoud Abdul-Rauf</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>Denver Nuggets</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>Center Stage</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr"/>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>Clifford Robinson</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>Portland Trail Blazers</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>Center Stage</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr"/>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>Chris Webber</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>Golden State Warriors</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>Draft Picks</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr"/>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>Shawn Bradley</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>Philadelphia 76ers</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>Draft Picks</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr"/>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>Anfernee Hardaway</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>Orlando Magic</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>Draft Picks</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr"/>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>Jamal Mashburn</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>Dallas Mavericks</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>Draft Picks</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr"/>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>Isaiah Rider</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>Minnesota Timberwolves</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>Draft Picks</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr"/>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>Calbert Cheaney</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>Washington Bullets</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>Draft Picks</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr"/>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>Bobby Hurley</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>Sacramento Kings</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>Draft Picks</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr"/>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>Vin Baker</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>Milwaukee Bucks</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>Draft Picks</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr"/>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>Rodney Rogers</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>Denver Nuggets</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>Draft Picks</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr"/>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>Lindsey Hunter</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>Detroit Pistons</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>Draft Picks</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr"/>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>Allan Houston</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>Detroit Pistons</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>Draft Picks</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr"/>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>George Lynch</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>Los Angeles Lakers</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>Draft Picks</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr"/>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>Terry Dehere</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>Los Angeles Clippers</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>Draft Picks</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr"/>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>Scott Haskin</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>Indiana Pacers</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>Draft Picks</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr"/>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>Doug Edwards</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>Atlanta Hawks</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>Draft Picks</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr"/>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>Rex Walters</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>New Jersey Nets</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>Draft Picks</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr"/>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>Greg Graham</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>Philadelphia 76ers</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>Draft Picks</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr"/>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>Luther Wright</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>Utah Jazz</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>Draft Picks</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr"/>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>Acie Earl</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>Boston Celtics</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>Draft Picks</t>
+        </is>
+      </c>
+      <c r="D366" t="inlineStr"/>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>Scott Burrell</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>Charlotte Hornets</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>Draft Picks</t>
+        </is>
+      </c>
+      <c r="D367" t="inlineStr"/>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>James Robinson</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>Portland Trail Blazers</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>Draft Picks</t>
+        </is>
+      </c>
+      <c r="D368" t="inlineStr"/>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>Chris Mills</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>Cleveland Cavaliers</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>Draft Picks</t>
+        </is>
+      </c>
+      <c r="D369" t="inlineStr"/>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>Ervin Johnson</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>Seattle SuperSonics</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>Draft Picks</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr"/>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>Sam Cassell</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>Houston Rockets</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>Draft Picks</t>
+        </is>
+      </c>
+      <c r="D371" t="inlineStr"/>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>Corie Blount</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>Chicago Bulls</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>Draft Picks</t>
+        </is>
+      </c>
+      <c r="D372" t="inlineStr"/>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>Malcolm Mackey</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>Phoenix Suns</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>Draft Picks</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr"/>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>Nick Anderson</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>Orlando Magic</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>Dynamic Dunks</t>
+        </is>
+      </c>
+      <c r="D374" t="inlineStr"/>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>Charles Barkley</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>Phoenix Suns</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>Dynamic Dunks</t>
+        </is>
+      </c>
+      <c r="D375" t="inlineStr"/>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>Robert Horry</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>Houston Rockets</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>Dynamic Dunks</t>
+        </is>
+      </c>
+      <c r="D376" t="inlineStr"/>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>Michael Jordan</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>Chicago Bulls</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>Dynamic Dunks</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr"/>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>Shawn Kemp</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>Seattle SuperSonics</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>Dynamic Dunks</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr"/>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>Anthony Mason</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>New York Knicks</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>Dynamic Dunks</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr"/>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>Alonzo Mourning</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>Charlotte Hornets</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>Dynamic Dunks</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr"/>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>Hakeem Olajuwon</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>Houston Rockets</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>Dynamic Dunks</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr"/>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>Dominique Wilkins</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>Atlanta Hawks</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>Dynamic Dunks</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr"/>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>Shaquille O'Neal</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>Orlando Magic</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>NBA All-Rookie Team</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr"/>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>Alonzo Mourning</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>Charlotte Hornets</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>NBA All-Rookie Team</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr"/>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>Christian Laettner</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>Minnesota Timberwolves</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>NBA All-Rookie Team</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr"/>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>Tom Gugliotta</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>Washington Bullets</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>NBA All-Rookie Team</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr"/>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>LaPhonso Ellis</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>Denver Nuggets</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>NBA All-Rookie Team</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr"/>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>Shaquille O'Neal</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>Orlando Magic</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>Shaq Talk</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr"/>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>Shaquille O'Neal</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>Orlando Magic</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>Shaq Talk</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr"/>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>Shaquille O'Neal</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>Orlando Magic</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>Shaq Talk</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr"/>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>Shaquille O'Neal</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>Orlando Magic</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>Shaq Talk</t>
+        </is>
+      </c>
+      <c r="D391" t="inlineStr"/>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>Shaquille O'Neal</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>Orlando Magic</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>Shaq Talk</t>
+        </is>
+      </c>
+      <c r="D392" t="inlineStr"/>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>Shaquille O'Neal</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>Orlando Magic</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>Shaq Talk</t>
+        </is>
+      </c>
+      <c r="D393" t="inlineStr"/>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>Shaquille O'Neal</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>Orlando Magic</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>Shaq Talk</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr"/>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>Shaquille O'Neal</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>Orlando Magic</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>Shaq Talk</t>
+        </is>
+      </c>
+      <c r="D395" t="inlineStr"/>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>Shaquille O'Neal</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>Orlando Magic</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>Shaq Talk</t>
+        </is>
+      </c>
+      <c r="D396" t="inlineStr"/>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>Shaquille O'Neal</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>Orlando Magic</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>Shaq Talk</t>
+        </is>
+      </c>
+      <c r="D397" t="inlineStr"/>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>Alonzo Mourning / Patrick Ewing</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr"/>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>Showdown Series</t>
+        </is>
+      </c>
+      <c r="D398" t="inlineStr"/>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>Shaquille O'Neal / Patrick Ewing</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr"/>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>Showdown Series</t>
+        </is>
+      </c>
+      <c r="D399" t="inlineStr"/>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>Alonzo Mourning / Shaquille O'Neal</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr"/>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>Showdown Series</t>
+        </is>
+      </c>
+      <c r="D400" t="inlineStr"/>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>Hakeem Olajuwon / Dikembe Mutombo</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr"/>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>Showdown Series</t>
+        </is>
+      </c>
+      <c r="D401" t="inlineStr"/>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>David Robinson / Hakeem Olajuwon</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr"/>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>Showdown Series</t>
+        </is>
+      </c>
+      <c r="D402" t="inlineStr"/>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>David Robinson / Dikembe Mutombo</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr"/>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>Showdown Series</t>
+        </is>
+      </c>
+      <c r="D403" t="inlineStr"/>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>Shawn Kemp / Karl Malone</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr"/>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>Showdown Series</t>
+        </is>
+      </c>
+      <c r="D404" t="inlineStr"/>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>Larry Johnson / Charles Barkley</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr"/>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>Showdown Series</t>
+        </is>
+      </c>
+      <c r="D405" t="inlineStr"/>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>Dominique Wilkins / Scottie Pippen</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr"/>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>Showdown Series</t>
+        </is>
+      </c>
+      <c r="D406" t="inlineStr"/>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>Joe Dumars / Reggie Miller</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr"/>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>Showdown Series</t>
+        </is>
+      </c>
+      <c r="D407" t="inlineStr"/>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>Clyde Drexler / Michael Jordan</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr"/>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>Showdown Series</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr"/>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>Magic Johnson / Larry Bird</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr"/>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>Showdown Series</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr"/>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>Jamal Mashburn / Jim Jackson</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>Dallas Mavericks</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>Thunder and Lightning</t>
+        </is>
+      </c>
+      <c r="D410" t="inlineStr"/>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>Harold Miner / Steve Smith</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>Miami Heat</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>Thunder and Lightning</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr"/>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>Isaiah Rider / Micheal Williams</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>Minnesota Timberwolves</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>Thunder and Lightning</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr"/>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>Derrick Coleman / Kenny Anderson</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>New Jersey Nets</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>Thunder and Lightning</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr"/>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>Patrick Ewing / John Starks</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>New York Knicks</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>Thunder and Lightning</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr"/>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>Shaquille O'Neal / Anfernee Hardaway</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>Orlando Magic</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>Thunder and Lightning</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr"/>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>Shawn Bradley / Jeff Hornacek</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>Philadelphia 76ers</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>Thunder and Lightning</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr"/>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>Walt Williams / Bobby Hurley</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>Sacramento Kings</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>Thunder and Lightning</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr"/>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>Dennis Rodman / David Robinson</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>San Antonio Spurs</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>Thunder and Lightning</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr"/>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>Steve Smith / Magic Johnson EXCH</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>USA Tip-Off</t>
+        </is>
+      </c>
+      <c r="D419" t="inlineStr"/>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>Larry Johnson / Charles Barkley EXCH</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>USA Tip-Off</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr"/>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>Patrick Ewing / Alonzo Mourning EXCH</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>USA Tip-Off</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr"/>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>Shawn Kemp / Karl Malone EXCH</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>USA Tip-Off</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr"/>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>Chris Mullin / Dan Majerle EXCH</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>USA Tip-Off</t>
+        </is>
+      </c>
+      <c r="D423" t="inlineStr"/>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>John Stockton / Mark Price EXCH</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>USA Tip-Off</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr"/>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>Christian Laettner / Derrick Coleman EXCH</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>USA Tip-Off</t>
+        </is>
+      </c>
+      <c r="D425" t="inlineStr"/>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>Dominique Wilkins / Clyde Drexler EXCH</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>USA Tip-Off</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr"/>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>Joe Dumars / Scottie Pippen EXCH</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>USA Tip-Off</t>
+        </is>
+      </c>
+      <c r="D427" t="inlineStr"/>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>David Robinson / Shaquille O'Neal EXCH</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>USA Tip-Off</t>
+        </is>
+      </c>
+      <c r="D428" t="inlineStr"/>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>Reggie Miller / Larry Bird EXCH</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>USA Tip-Off</t>
+        </is>
+      </c>
+      <c r="D429" t="inlineStr"/>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>Tim Hardaway</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>USA Tip-Off - EXCH</t>
+        </is>
+      </c>
+      <c r="D430" t="inlineStr"/>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>Isiah Thomas</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>USA Tip-Off - EXCH</t>
+        </is>
+      </c>
+      <c r="D431" t="inlineStr"/>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>Steve Smith / Magic Johnson EXCH</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>USA Tip-Off Gold</t>
+        </is>
+      </c>
+      <c r="D432" t="inlineStr"/>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>Larry Johnson / Charles Barkley EXCH</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>USA Tip-Off Gold</t>
+        </is>
+      </c>
+      <c r="D433" t="inlineStr"/>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>Patrick Ewing / Alonzo Mourning EXCH</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>USA Tip-Off Gold</t>
+        </is>
+      </c>
+      <c r="D434" t="inlineStr"/>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>Shawn Kemp / Karl Malone EXCH</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>USA Tip-Off Gold</t>
+        </is>
+      </c>
+      <c r="D435" t="inlineStr"/>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>Chris Mullin / Dan Majerle EXCH</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>USA Tip-Off Gold</t>
+        </is>
+      </c>
+      <c r="D436" t="inlineStr"/>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>John Stockton / Mark Price EXCH</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>USA Tip-Off Gold</t>
+        </is>
+      </c>
+      <c r="D437" t="inlineStr"/>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>Christian Laettner / Derrick Coleman EXCH</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>USA Tip-Off Gold</t>
+        </is>
+      </c>
+      <c r="D438" t="inlineStr"/>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>Dominique Wilkins / Clyde Drexler EXCH</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>USA Tip-Off Gold</t>
+        </is>
+      </c>
+      <c r="D439" t="inlineStr"/>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>Joe Dumars / Scottie Pippen EXCH</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>USA Tip-Off Gold</t>
+        </is>
+      </c>
+      <c r="D440" t="inlineStr"/>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>David Robinson / Shaquille O'Neal EXCH</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>USA Tip-Off Gold</t>
+        </is>
+      </c>
+      <c r="D441" t="inlineStr"/>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>Reggie Miller / Larry Bird EXCH</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>USA Tip-Off Gold</t>
+        </is>
+      </c>
+      <c r="D442" t="inlineStr"/>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>Tim Hardaway</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>USA Tip-Off Gold - EXCH</t>
+        </is>
+      </c>
+      <c r="D443" t="inlineStr"/>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>Isiah Thomas</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>USA Tip-Off Gold - EXCH</t>
+        </is>
+      </c>
+      <c r="D444" t="inlineStr"/>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>Tom Gugliotta</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>Washington Bullets</t>
+        </is>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>Promos</t>
+        </is>
+      </c>
+      <c r="D445" t="inlineStr"/>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>Larry Johnson</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>Charlotte Hornets</t>
+        </is>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>Promos</t>
+        </is>
+      </c>
+      <c r="D446" t="inlineStr"/>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>Michael Jordan</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>Chicago Bulls</t>
+        </is>
+      </c>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>Promos</t>
+        </is>
+      </c>
+      <c r="D447" t="inlineStr"/>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>Christian Laettner</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>Minnesota Timberwolves</t>
+        </is>
+      </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>Promos</t>
+        </is>
+      </c>
+      <c r="D448" t="inlineStr"/>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>Dan Majerle</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>Phoenix Suns</t>
+        </is>
+      </c>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>Promos</t>
+        </is>
+      </c>
+      <c r="D449" t="inlineStr"/>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>Alonzo Mourning / Patrick Ewing</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr"/>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>Promos</t>
+        </is>
+      </c>
+      <c r="D450" t="inlineStr"/>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>Shaquille O'Neal</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>Orlando Magic</t>
+        </is>
+      </c>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>Promos - Center Stage</t>
+        </is>
+      </c>
+      <c r="D451" t="inlineStr"/>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>David Robinson</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>San Antonio Spurs</t>
+        </is>
+      </c>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>Promos</t>
+        </is>
+      </c>
+      <c r="D452" t="inlineStr"/>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>Steve Smith</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>Miami Heat</t>
+        </is>
+      </c>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t>Promos</t>
+        </is>
+      </c>
+      <c r="D453" t="inlineStr"/>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>Randy Woods</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>Los Angeles Clippers</t>
+        </is>
+      </c>
+      <c r="C454" t="inlineStr">
+        <is>
+          <t>Promos</t>
+        </is>
+      </c>
+      <c r="D454" t="inlineStr"/>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>Isiah Thomas</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>Detroit Pistons</t>
+        </is>
+      </c>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t>Series 1 Perforated Sheet 1</t>
+        </is>
+      </c>
+      <c r="D455" t="inlineStr"/>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>Larry Johnson</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>Charlotte Hornets</t>
+        </is>
+      </c>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t>Series 1 Perforated Sheet 1</t>
+        </is>
+      </c>
+      <c r="D456" t="inlineStr"/>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>Loy Vaught</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>Los Angeles Clippers</t>
+        </is>
+      </c>
+      <c r="C457" t="inlineStr">
+        <is>
+          <t>Series 1 Perforated Sheet 1</t>
+        </is>
+      </c>
+      <c r="D457" t="inlineStr"/>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>Mahmoud Abdul-Rauf</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>Denver Nuggets</t>
+        </is>
+      </c>
+      <c r="C458" t="inlineStr">
+        <is>
+          <t>Series 1 Perforated Sheet 1</t>
+        </is>
+      </c>
+      <c r="D458" t="inlineStr"/>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>Mark Price</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>Cleveland Cavaliers</t>
+        </is>
+      </c>
+      <c r="C459" t="inlineStr">
+        <is>
+          <t>Series 1 Perforated Sheet 1</t>
+        </is>
+      </c>
+      <c r="D459" t="inlineStr"/>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>Xavier McDaniel</t>
+        </is>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>Boston Celtics</t>
+        </is>
+      </c>
+      <c r="C460" t="inlineStr">
+        <is>
+          <t>Series 1 Perforated Sheet 1</t>
+        </is>
+      </c>
+      <c r="D460" t="inlineStr"/>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>Isiah Thomas / Larry Johnson / Loy Vaught / Mahmoud Abdul-Rauf / Mark Price / Xavier McDaniel</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr"/>
+      <c r="C461" t="inlineStr">
+        <is>
+          <t>Series 1 Perforated Sheet 1</t>
+        </is>
+      </c>
+      <c r="D461" t="inlineStr"/>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>Kenny Anderson</t>
+        </is>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>New Jersey Nets</t>
+        </is>
+      </c>
+      <c r="C462" t="inlineStr">
+        <is>
+          <t>Series 1 Perforated Sheet 2</t>
+        </is>
+      </c>
+      <c r="D462" t="inlineStr"/>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>Terrell Brandon</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>Cleveland Cavaliers</t>
+        </is>
+      </c>
+      <c r="C463" t="inlineStr">
+        <is>
+          <t>Series 1 Perforated Sheet 2</t>
+        </is>
+      </c>
+      <c r="D463" t="inlineStr"/>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>John Paxson</t>
+        </is>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>Chicago Bulls</t>
+        </is>
+      </c>
+      <c r="C464" t="inlineStr">
+        <is>
+          <t>Series 1 Perforated Sheet 2</t>
+        </is>
+      </c>
+      <c r="D464" t="inlineStr"/>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>Doug Smith</t>
+        </is>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>Dallas Mavericks</t>
+        </is>
+      </c>
+      <c r="C465" t="inlineStr">
+        <is>
+          <t>Series 1 Perforated Sheet 2</t>
+        </is>
+      </c>
+      <c r="D465" t="inlineStr"/>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>Dominique Wilkins</t>
+        </is>
+      </c>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>Atlanta Hawks</t>
+        </is>
+      </c>
+      <c r="C466" t="inlineStr">
+        <is>
+          <t>Series 1 Perforated Sheet 2</t>
+        </is>
+      </c>
+      <c r="D466" t="inlineStr"/>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>James Worthy</t>
+        </is>
+      </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>Los Angeles Lakers</t>
+        </is>
+      </c>
+      <c r="C467" t="inlineStr">
+        <is>
+          <t>Series 1 Perforated Sheet 2</t>
+        </is>
+      </c>
+      <c r="D467" t="inlineStr"/>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>Kenny Anderson / Terrell Brandon / John Paxson / Doug Smith / Dominique Wilkins / James Worthy Cards Originally Distributed as an Uncut Sheet in Magazines</t>
+        </is>
+      </c>
+      <c r="B468" t="inlineStr"/>
+      <c r="C468" t="inlineStr">
+        <is>
+          <t>Series 1 Perforated Sheet 2</t>
+        </is>
+      </c>
+      <c r="D468" t="inlineStr"/>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>Stacey Augmon</t>
+        </is>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>Atlanta Hawks</t>
+        </is>
+      </c>
+      <c r="C469" t="inlineStr">
+        <is>
+          <t>Series 1 Perforated Sheet 3</t>
+        </is>
+      </c>
+      <c r="D469" t="inlineStr"/>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>Dee Brown</t>
+        </is>
+      </c>
+      <c r="B470" t="inlineStr">
+        <is>
+          <t>Boston Celtics</t>
+        </is>
+      </c>
+      <c r="C470" t="inlineStr">
+        <is>
+          <t>Series 1 Perforated Sheet 3</t>
+        </is>
+      </c>
+      <c r="D470" t="inlineStr"/>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>Laphonso Ellis</t>
+        </is>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>Denver Nuggets</t>
+        </is>
+      </c>
+      <c r="C471" t="inlineStr">
+        <is>
+          <t>Series 1 Perforated Sheet 3</t>
+        </is>
+      </c>
+      <c r="D471" t="inlineStr"/>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>Tim Hardaway</t>
+        </is>
+      </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>Golden State Warriors</t>
+        </is>
+      </c>
+      <c r="C472" t="inlineStr">
+        <is>
+          <t>Series 1 Perforated Sheet 3</t>
+        </is>
+      </c>
+      <c r="D472" t="inlineStr"/>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>Dan Majerle</t>
+        </is>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>Phoenix Suns</t>
+        </is>
+      </c>
+      <c r="C473" t="inlineStr">
+        <is>
+          <t>Series 1 Perforated Sheet 3</t>
+        </is>
+      </c>
+      <c r="D473" t="inlineStr"/>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>Alonzo Mourning</t>
+        </is>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>Charlotte Hornets</t>
+        </is>
+      </c>
+      <c r="C474" t="inlineStr">
+        <is>
+          <t>Series 1 Perforated Sheet 3</t>
+        </is>
+      </c>
+      <c r="D474" t="inlineStr"/>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>Stacey Augmon / Dee Brown / Laphonso Ellis / Tim Hardaway / Dan Majerle / Alonzo Mourning Cards Originally Distributed in Uncut Sheets in Magazines</t>
+        </is>
+      </c>
+      <c r="B475" t="inlineStr"/>
+      <c r="C475" t="inlineStr">
+        <is>
+          <t>Series 1 Perforated Sheet 3</t>
+        </is>
+      </c>
+      <c r="D475" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
